--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -1,21 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cuong\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315EA309-7570-42DF-843D-E551DC84E0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
+  <workbookPr/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C2BD6EF-A63E-4C5D-B82C-57B941F90246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{49A23A8D-3308-41CA-92E7-37734359631B}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,42 +31,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
+  <si>
+    <t>Tên lái xe</t>
+  </si>
+  <si>
+    <t>CMND/CCCD</t>
+  </si>
+  <si>
+    <t>Biến số xe</t>
+  </si>
+  <si>
+    <t>Tải trọng</t>
+  </si>
+  <si>
+    <t>Cổng vào</t>
+  </si>
+  <si>
+    <t>Thời gian dự kiến vào </t>
+  </si>
   <si>
     <t>Ghi chú</t>
   </si>
   <si>
+    <t>Phạm Mạnh Cường</t>
+  </si>
+  <si>
+    <t>20C-00735</t>
+  </si>
+  <si>
     <t>Xe chở container 40'-45' hoặc xe trên 10 tấn và xe rơ móoc</t>
   </si>
   <si>
-    <t>Tải trọng</t>
-  </si>
-  <si>
-    <t>Cổng vào</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thời gian dự kiến vào </t>
-  </si>
-  <si>
-    <t>Biến số xe</t>
-  </si>
-  <si>
-    <t>CMND/CCCD</t>
-  </si>
-  <si>
-    <t>Tên lái xe</t>
-  </si>
-  <si>
-    <t>370996688114</t>
-  </si>
-  <si>
-    <t>Phạm Mạnh Cường</t>
-  </si>
-  <si>
     <t>Cổng 3</t>
   </si>
   <si>
-    <t>20C-00735</t>
+    <t> </t>
   </si>
   <si>
     <t>Phạm Mạnh A</t>
@@ -81,29 +76,13 @@
   </si>
   <si>
     <t>Phạm Mạnh C</t>
-  </si>
-  <si>
-    <t>22/13/2025 12:30</t>
-  </si>
-  <si>
-    <t>22/13/2025 12:31</t>
-  </si>
-  <si>
-    <t>22/13/2025 12:32</t>
-  </si>
-  <si>
-    <t>22/13/2025 12:33</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="00000"/>
-    <numFmt numFmtId="165" formatCode="[$-101042A]d/m/yyyy\ h:mm\ AM/PM;@"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,10 +91,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -126,7 +106,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -149,26 +129,66 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -197,13 +217,13 @@
         <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="145F82"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="E87331"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="186C24"/>
       </a:accent3>
       <a:accent4>
         <a:srgbClr val="0F9ED5"/>
@@ -223,7 +243,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -489,166 +509,140 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D7C23A9-07B5-4A5E-AEAF-C43FE9E711E2}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.5703125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="29.25">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
+      <c r="B2" s="4">
+        <v>370996688114</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="7">
+        <v>46013</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="3" spans="1:7" ht="29.25">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4">
+        <v>370996688114</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="7">
+        <v>46013</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="29.25">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4">
+        <v>370996688114</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="7">
+        <v>46015</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1" t="s">
+    </row>
+    <row r="5" spans="1:7" ht="29.25">
+      <c r="A5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4">
+        <v>370996688114</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="F5" s="7">
+        <v>46016</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B6"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B8"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B9"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B10"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B13"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D5" xr:uid="{0125AE67-6B26-43FB-AE4B-0B14A7DCB6BF}">
-      <formula1>"Xe ô tô 17-29 chỗ và Xe tải tên 3.5 tấn đến 7, Xe chở container 40'-45' hoặc xe trên 10 tấn và xe rơ móoc"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E5" xr:uid="{9CA22730-FD37-4FC7-9FC5-9246CBAC8461}">
-      <formula1>"Cổng 1, Cổng 2, Cổng 3"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>